--- a/INVENTORY MANAGEMENT.xlsx
+++ b/INVENTORY MANAGEMENT.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="827" documentId="8_{FE73C578-B731-4C19-8129-3C01BD6B95D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A4AAB90-7725-4376-AE33-4EB2E17E1A20}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B5AE7B4-5B13-4B27-A4C2-DD555712B40E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{7B5AE7B4-5B13-4B27-A4C2-DD555712B40E}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="1" r:id="rId1"/>
@@ -2367,17 +2367,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G315"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="5" width="22.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="4" max="5" width="22.1796875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>35</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>39</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>44</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>48</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>50</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>52</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>54</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>56</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>60</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>62</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>67</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
         <v>69</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
         <v>71</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>73</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>79</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>82</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>85</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>91</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>94</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>97</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>99</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>102</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>105</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>107</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>109</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>111</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>114</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>117</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>120</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>123</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>126</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>130</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>132</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>135</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>138</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>141</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>144</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>147</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>150</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>153</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>155</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>158</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>160</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>162</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>164</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>166</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>168</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>170</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>173</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>176</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>178</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>180</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>184</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>187</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>189</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>191</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>194</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>197</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>200</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>203</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>205</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>207</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>210</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>212</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>215</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>218</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>220</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>222</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>225</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>227</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>230</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>233</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>236</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>238</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>241</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>244</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>246</v>
       </c>
@@ -4602,7 +4602,7 @@
       <c r="F97" s="7"/>
       <c r="G97" s="15"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>248</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="F98" s="7"/>
       <c r="G98" s="15"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>250</v>
       </c>
@@ -4636,7 +4636,7 @@
       <c r="F99" s="7"/>
       <c r="G99" s="15"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>253</v>
       </c>
@@ -4653,7 +4653,7 @@
       <c r="F100" s="7"/>
       <c r="G100" s="15"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>255</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="F101" s="7"/>
       <c r="G101" s="15"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>257</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="F102" s="7"/>
       <c r="G102" s="15"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>259</v>
       </c>
@@ -4704,7 +4704,7 @@
       <c r="F103" s="7"/>
       <c r="G103" s="15"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>261</v>
       </c>
@@ -4721,7 +4721,7 @@
       <c r="F104" s="7"/>
       <c r="G104" s="15"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>263</v>
       </c>
@@ -4738,7 +4738,7 @@
       <c r="F105" s="7"/>
       <c r="G105" s="15"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>265</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="F106" s="7"/>
       <c r="G106" s="15"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>267</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="F107" s="7"/>
       <c r="G107" s="15"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="str">
         <f>LEFT(A107, LEN(A107)-3) &amp; TEXT(RIGHT(A107, 3) + 1, "000")</f>
         <v>NFAL0018</v>
@@ -4790,7 +4790,7 @@
       <c r="F108" s="7"/>
       <c r="G108" s="15"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="str">
         <f t="shared" ref="A109:A139" si="0">LEFT(A108, LEN(A108)-3) &amp; TEXT(RIGHT(A108, 3) + 1, "000")</f>
         <v>NFAL0019</v>
@@ -4808,7 +4808,7 @@
       <c r="F109" s="7"/>
       <c r="G109" s="15"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0020</v>
@@ -4826,7 +4826,7 @@
       <c r="F110" s="7"/>
       <c r="G110" s="15"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0021</v>
@@ -4844,7 +4844,7 @@
       <c r="F111" s="7"/>
       <c r="G111" s="15"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0022</v>
@@ -4862,7 +4862,7 @@
       <c r="F112" s="7"/>
       <c r="G112" s="15"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0023</v>
@@ -4880,7 +4880,7 @@
       <c r="F113" s="7"/>
       <c r="G113" s="15"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0024</v>
@@ -4898,7 +4898,7 @@
       <c r="F114" s="7"/>
       <c r="G114" s="15"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0025</v>
@@ -4916,7 +4916,7 @@
       <c r="F115" s="7"/>
       <c r="G115" s="15"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0026</v>
@@ -4934,7 +4934,7 @@
       <c r="F116" s="7"/>
       <c r="G116" s="15"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0027</v>
@@ -4952,7 +4952,7 @@
       <c r="F117" s="7"/>
       <c r="G117" s="15"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0028</v>
@@ -4970,7 +4970,7 @@
       <c r="F118" s="7"/>
       <c r="G118" s="15"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0029</v>
@@ -4988,7 +4988,7 @@
       <c r="F119" s="7"/>
       <c r="G119" s="15"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0030</v>
@@ -5006,7 +5006,7 @@
       <c r="F120" s="7"/>
       <c r="G120" s="15"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0031</v>
@@ -5024,7 +5024,7 @@
       <c r="F121" s="7"/>
       <c r="G121" s="15"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0032</v>
@@ -5042,7 +5042,7 @@
       <c r="F122" s="7"/>
       <c r="G122" s="15"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0033</v>
@@ -5060,7 +5060,7 @@
       <c r="F123" s="7"/>
       <c r="G123" s="15"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0034</v>
@@ -5078,7 +5078,7 @@
       <c r="F124" s="7"/>
       <c r="G124" s="15"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0035</v>
@@ -5096,7 +5096,7 @@
       <c r="F125" s="7"/>
       <c r="G125" s="15"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0036</v>
@@ -5114,7 +5114,7 @@
       <c r="F126" s="7"/>
       <c r="G126" s="15"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0037</v>
@@ -5132,7 +5132,7 @@
       <c r="F127" s="7"/>
       <c r="G127" s="15"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0038</v>
@@ -5150,7 +5150,7 @@
       <c r="F128" s="7"/>
       <c r="G128" s="15"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0039</v>
@@ -5168,7 +5168,7 @@
       <c r="F129" s="7"/>
       <c r="G129" s="15"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0040</v>
@@ -5186,7 +5186,7 @@
       <c r="F130" s="7"/>
       <c r="G130" s="15"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0041</v>
@@ -5204,7 +5204,7 @@
       <c r="F131" s="7"/>
       <c r="G131" s="15"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0042</v>
@@ -5222,7 +5222,7 @@
       <c r="F132" s="7"/>
       <c r="G132" s="15"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0043</v>
@@ -5240,7 +5240,7 @@
       <c r="F133" s="7"/>
       <c r="G133" s="15"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0044</v>
@@ -5258,7 +5258,7 @@
       <c r="F134" s="7"/>
       <c r="G134" s="15"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0045</v>
@@ -5276,7 +5276,7 @@
       <c r="F135" s="7"/>
       <c r="G135" s="15"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0046</v>
@@ -5294,7 +5294,7 @@
       <c r="F136" s="7"/>
       <c r="G136" s="15"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0047</v>
@@ -5312,7 +5312,7 @@
       <c r="F137" s="7"/>
       <c r="G137" s="15"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0048</v>
@@ -5330,7 +5330,7 @@
       <c r="F138" s="7"/>
       <c r="G138" s="15"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NFAL0049</v>
@@ -5348,7 +5348,7 @@
       <c r="F139" s="7"/>
       <c r="G139" s="15"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>301</v>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="F140" s="7"/>
       <c r="G140" s="15"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>303</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="F141" s="7"/>
       <c r="G141" s="15"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>305</v>
       </c>
@@ -5399,7 +5399,7 @@
       <c r="F142" s="7"/>
       <c r="G142" s="15"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>307</v>
       </c>
@@ -5416,7 +5416,7 @@
       <c r="F143" s="7"/>
       <c r="G143" s="15"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>309</v>
       </c>
@@ -5433,7 +5433,7 @@
       <c r="F144" s="7"/>
       <c r="G144" s="15"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>311</v>
       </c>
@@ -5450,7 +5450,7 @@
       <c r="F145" s="7"/>
       <c r="G145" s="15"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>313</v>
       </c>
@@ -5467,7 +5467,7 @@
       <c r="F146" s="7"/>
       <c r="G146" s="15"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>315</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="F147" s="7"/>
       <c r="G147" s="15"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>317</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="F148" s="7"/>
       <c r="G148" s="15"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>319</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="F149" s="7"/>
       <c r="G149" s="15"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>321</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="F150" s="7"/>
       <c r="G150" s="15"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>323</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="F151" s="7"/>
       <c r="G151" s="15"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>325</v>
       </c>
@@ -5569,7 +5569,7 @@
       <c r="F152" s="7"/>
       <c r="G152" s="15"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>327</v>
       </c>
@@ -5586,7 +5586,7 @@
       <c r="F153" s="7"/>
       <c r="G153" s="15"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>329</v>
       </c>
@@ -5603,7 +5603,7 @@
       <c r="F154" s="7"/>
       <c r="G154" s="15"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>331</v>
       </c>
@@ -5620,7 +5620,7 @@
       <c r="F155" s="7"/>
       <c r="G155" s="15"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>333</v>
       </c>
@@ -5637,7 +5637,7 @@
       <c r="F156" s="7"/>
       <c r="G156" s="15"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>335</v>
       </c>
@@ -5654,7 +5654,7 @@
       <c r="F157" s="7"/>
       <c r="G157" s="15"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>337</v>
       </c>
@@ -5671,7 +5671,7 @@
       <c r="F158" s="7"/>
       <c r="G158" s="15"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>339</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="F159" s="7"/>
       <c r="G159" s="15"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>341</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="F160" s="7"/>
       <c r="G160" s="15"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>343</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="F161" s="7"/>
       <c r="G161" s="15"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>345</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="F162" s="7"/>
       <c r="G162" s="15"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>347</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="F163" s="7"/>
       <c r="G163" s="15"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>349</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="F164" s="7"/>
       <c r="G164" s="15"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>351</v>
       </c>
@@ -5790,7 +5790,7 @@
       <c r="F165" s="7"/>
       <c r="G165" s="15"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>353</v>
       </c>
@@ -5807,7 +5807,7 @@
       <c r="F166" s="7"/>
       <c r="G166" s="15"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>355</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="F167" s="7"/>
       <c r="G167" s="15"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>357</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="F168" s="7"/>
       <c r="G168" s="15"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>359</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="F169" s="7"/>
       <c r="G169" s="15"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>361</v>
       </c>
@@ -5875,7 +5875,7 @@
       <c r="F170" s="7"/>
       <c r="G170" s="15"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>363</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="F171" s="7"/>
       <c r="G171" s="15"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>365</v>
       </c>
@@ -5909,7 +5909,7 @@
       <c r="F172" s="7"/>
       <c r="G172" s="15"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>367</v>
       </c>
@@ -5926,7 +5926,7 @@
       <c r="F173" s="7"/>
       <c r="G173" s="15"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>369</v>
       </c>
@@ -5943,7 +5943,7 @@
       <c r="F174" s="7"/>
       <c r="G174" s="15"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>371</v>
       </c>
@@ -5960,7 +5960,7 @@
       <c r="F175" s="7"/>
       <c r="G175" s="15"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>373</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="F176" s="7"/>
       <c r="G176" s="15"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>375</v>
       </c>
@@ -5994,7 +5994,7 @@
       <c r="F177" s="7"/>
       <c r="G177" s="15"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>377</v>
       </c>
@@ -6011,7 +6011,7 @@
       <c r="F178" s="7"/>
       <c r="G178" s="15"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>379</v>
       </c>
@@ -6028,7 +6028,7 @@
       <c r="F179" s="7"/>
       <c r="G179" s="15"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>381</v>
       </c>
@@ -6045,7 +6045,7 @@
       <c r="F180" s="7"/>
       <c r="G180" s="15"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>383</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="F181" s="7"/>
       <c r="G181" s="15"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="5" t="s">
         <v>385</v>
@@ -6077,7 +6077,7 @@
       <c r="F182" s="7"/>
       <c r="G182" s="15"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>388</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="F183" s="7"/>
       <c r="G183" s="15"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>390</v>
       </c>
@@ -6111,7 +6111,7 @@
       <c r="F184" s="7"/>
       <c r="G184" s="15"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>392</v>
       </c>
@@ -6128,7 +6128,7 @@
       <c r="F185" s="7"/>
       <c r="G185" s="15"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>394</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="F186" s="7"/>
       <c r="G186" s="15"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>397</v>
       </c>
@@ -6162,7 +6162,7 @@
       <c r="F187" s="7"/>
       <c r="G187" s="15"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>399</v>
       </c>
@@ -6179,7 +6179,7 @@
       <c r="F188" s="7"/>
       <c r="G188" s="15"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>401</v>
       </c>
@@ -6196,7 +6196,7 @@
       <c r="F189" s="7"/>
       <c r="G189" s="15"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>403</v>
       </c>
@@ -6213,7 +6213,7 @@
       <c r="F190" s="7"/>
       <c r="G190" s="15"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>405</v>
       </c>
@@ -6230,7 +6230,7 @@
       <c r="F191" s="7"/>
       <c r="G191" s="15"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>408</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="F192" s="7"/>
       <c r="G192" s="15"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="5" t="s">
         <v>410</v>
@@ -6262,7 +6262,7 @@
       <c r="F193" s="7"/>
       <c r="G193" s="15"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>411</v>
       </c>
@@ -6279,7 +6279,7 @@
       <c r="F194" s="7"/>
       <c r="G194" s="15"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>413</v>
       </c>
@@ -6296,7 +6296,7 @@
       <c r="F195" s="7"/>
       <c r="G195" s="15"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="5" t="s">
         <v>415</v>
@@ -6311,7 +6311,7 @@
       <c r="F196" s="7"/>
       <c r="G196" s="15"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>417</v>
       </c>
@@ -6328,7 +6328,7 @@
       <c r="F197" s="7"/>
       <c r="G197" s="15"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>419</v>
       </c>
@@ -6345,7 +6345,7 @@
       <c r="F198" s="7"/>
       <c r="G198" s="15"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>421</v>
       </c>
@@ -6362,7 +6362,7 @@
       <c r="F199" s="7"/>
       <c r="G199" s="15"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>423</v>
       </c>
@@ -6379,7 +6379,7 @@
       <c r="F200" s="7"/>
       <c r="G200" s="15"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>425</v>
       </c>
@@ -6396,7 +6396,7 @@
       <c r="F201" s="7"/>
       <c r="G201" s="15"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>427</v>
       </c>
@@ -6413,7 +6413,7 @@
       <c r="F202" s="7"/>
       <c r="G202" s="15"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>429</v>
       </c>
@@ -6430,7 +6430,7 @@
       <c r="F203" s="7"/>
       <c r="G203" s="15"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>431</v>
       </c>
@@ -6447,7 +6447,7 @@
       <c r="F204" s="7"/>
       <c r="G204" s="15"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="5" t="s">
         <v>433</v>
@@ -6462,7 +6462,7 @@
       <c r="F205" s="7"/>
       <c r="G205" s="15"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>434</v>
       </c>
@@ -6479,7 +6479,7 @@
       <c r="F206" s="7"/>
       <c r="G206" s="15"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>436</v>
       </c>
@@ -6496,7 +6496,7 @@
       <c r="F207" s="7"/>
       <c r="G207" s="15"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="str">
         <f>LEFT(A207, LEN(A207)-3) &amp; TEXT(RIGHT(A207, 3) + 1, "000")</f>
         <v>NFSS023</v>
@@ -6514,7 +6514,7 @@
       <c r="F208" s="7"/>
       <c r="G208" s="15"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="str">
         <f t="shared" ref="A209:A239" si="1">LEFT(A208, LEN(A208)-3) &amp; TEXT(RIGHT(A208, 3) + 1, "000")</f>
         <v>NFSS024</v>
@@ -6532,7 +6532,7 @@
       <c r="F209" s="7"/>
       <c r="G209" s="15"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS025</v>
@@ -6550,7 +6550,7 @@
       <c r="F210" s="7"/>
       <c r="G210" s="15"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS026</v>
@@ -6568,7 +6568,7 @@
       <c r="F211" s="7"/>
       <c r="G211" s="15"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS027</v>
@@ -6586,7 +6586,7 @@
       <c r="F212" s="7"/>
       <c r="G212" s="15"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS028</v>
@@ -6604,7 +6604,7 @@
       <c r="F213" s="7"/>
       <c r="G213" s="15"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS029</v>
@@ -6622,7 +6622,7 @@
       <c r="F214" s="7"/>
       <c r="G214" s="15"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS030</v>
@@ -6640,7 +6640,7 @@
       <c r="F215" s="7"/>
       <c r="G215" s="15"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS031</v>
@@ -6658,7 +6658,7 @@
       <c r="F216" s="7"/>
       <c r="G216" s="15"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS032</v>
@@ -6676,7 +6676,7 @@
       <c r="F217" s="7"/>
       <c r="G217" s="15"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS033</v>
@@ -6694,7 +6694,7 @@
       <c r="F218" s="7"/>
       <c r="G218" s="15"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS034</v>
@@ -6712,7 +6712,7 @@
       <c r="F219" s="7"/>
       <c r="G219" s="15"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS035</v>
@@ -6730,7 +6730,7 @@
       <c r="F220" s="7"/>
       <c r="G220" s="15"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS036</v>
@@ -6748,7 +6748,7 @@
       <c r="F221" s="7"/>
       <c r="G221" s="15"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS037</v>
@@ -6766,7 +6766,7 @@
       <c r="F222" s="7"/>
       <c r="G222" s="15"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS038</v>
@@ -6784,7 +6784,7 @@
       <c r="F223" s="7"/>
       <c r="G223" s="15"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS039</v>
@@ -6802,7 +6802,7 @@
       <c r="F224" s="7"/>
       <c r="G224" s="15"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS040</v>
@@ -6820,7 +6820,7 @@
       <c r="F225" s="7"/>
       <c r="G225" s="15"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS041</v>
@@ -6838,7 +6838,7 @@
       <c r="F226" s="7"/>
       <c r="G226" s="15"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS042</v>
@@ -6856,7 +6856,7 @@
       <c r="F227" s="7"/>
       <c r="G227" s="15"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS043</v>
@@ -6874,7 +6874,7 @@
       <c r="F228" s="7"/>
       <c r="G228" s="15"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS044</v>
@@ -6892,7 +6892,7 @@
       <c r="F229" s="7"/>
       <c r="G229" s="15"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS045</v>
@@ -6910,7 +6910,7 @@
       <c r="F230" s="7"/>
       <c r="G230" s="15"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS046</v>
@@ -6928,7 +6928,7 @@
       <c r="F231" s="7"/>
       <c r="G231" s="15"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS047</v>
@@ -6946,7 +6946,7 @@
       <c r="F232" s="7"/>
       <c r="G232" s="15"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS048</v>
@@ -6964,7 +6964,7 @@
       <c r="F233" s="7"/>
       <c r="G233" s="15"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS049</v>
@@ -6982,7 +6982,7 @@
       <c r="F234" s="7"/>
       <c r="G234" s="15"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS050</v>
@@ -7000,7 +7000,7 @@
       <c r="F235" s="7"/>
       <c r="G235" s="15"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS051</v>
@@ -7018,7 +7018,7 @@
       <c r="F236" s="7"/>
       <c r="G236" s="15"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS052</v>
@@ -7036,7 +7036,7 @@
       <c r="F237" s="7"/>
       <c r="G237" s="15"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS053</v>
@@ -7054,7 +7054,7 @@
       <c r="F238" s="7"/>
       <c r="G238" s="15"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>NFSS054</v>
@@ -7072,7 +7072,7 @@
       <c r="F239" s="7"/>
       <c r="G239" s="15"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>470</v>
       </c>
@@ -7089,7 +7089,7 @@
       <c r="F240" s="7"/>
       <c r="G240" s="15"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="5" t="s">
         <v>472</v>
@@ -7102,7 +7102,7 @@
       <c r="F241" s="7"/>
       <c r="G241" s="15"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>473</v>
       </c>
@@ -7119,7 +7119,7 @@
       <c r="F242" s="7"/>
       <c r="G242" s="15"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>476</v>
       </c>
@@ -7136,7 +7136,7 @@
       <c r="F243" s="7"/>
       <c r="G243" s="15"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>478</v>
       </c>
@@ -7153,7 +7153,7 @@
       <c r="F244" s="7"/>
       <c r="G244" s="15"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>480</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="F245" s="7"/>
       <c r="G245" s="15"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>483</v>
       </c>
@@ -7187,7 +7187,7 @@
       <c r="F246" s="7"/>
       <c r="G246" s="15"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>485</v>
       </c>
@@ -7204,7 +7204,7 @@
       <c r="F247" s="7"/>
       <c r="G247" s="15"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>487</v>
       </c>
@@ -7221,7 +7221,7 @@
       <c r="F248" s="7"/>
       <c r="G248" s="15"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>489</v>
       </c>
@@ -7238,7 +7238,7 @@
       <c r="F249" s="7"/>
       <c r="G249" s="15"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>491</v>
       </c>
@@ -7255,7 +7255,7 @@
       <c r="F250" s="7"/>
       <c r="G250" s="15"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>493</v>
       </c>
@@ -7272,7 +7272,7 @@
       <c r="F251" s="7"/>
       <c r="G251" s="15"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>495</v>
       </c>
@@ -7289,7 +7289,7 @@
       <c r="F252" s="7"/>
       <c r="G252" s="15"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>497</v>
       </c>
@@ -7306,7 +7306,7 @@
       <c r="F253" s="7"/>
       <c r="G253" s="15"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>500</v>
       </c>
@@ -7323,7 +7323,7 @@
       <c r="F254" s="7"/>
       <c r="G254" s="15"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>502</v>
       </c>
@@ -7340,7 +7340,7 @@
       <c r="F255" s="7"/>
       <c r="G255" s="15"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>504</v>
       </c>
@@ -7357,7 +7357,7 @@
       <c r="F256" s="7"/>
       <c r="G256" s="15"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>506</v>
       </c>
@@ -7374,7 +7374,7 @@
       <c r="F257" s="7"/>
       <c r="G257" s="15"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>508</v>
       </c>
@@ -7391,7 +7391,7 @@
       <c r="F258" s="7"/>
       <c r="G258" s="15"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>511</v>
       </c>
@@ -7408,7 +7408,7 @@
       <c r="F259" s="7"/>
       <c r="G259" s="15"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>513</v>
       </c>
@@ -7425,7 +7425,7 @@
       <c r="F260" s="7"/>
       <c r="G260" s="15"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>515</v>
       </c>
@@ -7442,7 +7442,7 @@
       <c r="F261" s="7"/>
       <c r="G261" s="15"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>517</v>
       </c>
@@ -7459,7 +7459,7 @@
       <c r="F262" s="7"/>
       <c r="G262" s="15"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>519</v>
       </c>
@@ -7476,7 +7476,7 @@
       <c r="F263" s="7"/>
       <c r="G263" s="15"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>521</v>
       </c>
@@ -7493,7 +7493,7 @@
       <c r="F264" s="7"/>
       <c r="G264" s="15"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>497</v>
       </c>
@@ -7510,7 +7510,7 @@
       <c r="F265" s="7"/>
       <c r="G265" s="15"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>524</v>
       </c>
@@ -7527,7 +7527,7 @@
       <c r="F266" s="7"/>
       <c r="G266" s="15"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>526</v>
       </c>
@@ -7544,7 +7544,7 @@
       <c r="F267" s="7"/>
       <c r="G267" s="15"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>528</v>
       </c>
@@ -7561,7 +7561,7 @@
       <c r="F268" s="7"/>
       <c r="G268" s="15"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>530</v>
       </c>
@@ -7578,7 +7578,7 @@
       <c r="F269" s="7"/>
       <c r="G269" s="15"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>532</v>
       </c>
@@ -7595,7 +7595,7 @@
       <c r="F270" s="7"/>
       <c r="G270" s="15"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>534</v>
       </c>
@@ -7612,7 +7612,7 @@
       <c r="F271" s="7"/>
       <c r="G271" s="15"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>416</v>
       </c>
@@ -7629,7 +7629,7 @@
       <c r="F272" s="7"/>
       <c r="G272" s="15"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>537</v>
       </c>
@@ -7646,7 +7646,7 @@
       <c r="F273" s="7"/>
       <c r="G273" s="15"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>539</v>
       </c>
@@ -7663,7 +7663,7 @@
       <c r="F274" s="7"/>
       <c r="G274" s="15"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>541</v>
       </c>
@@ -7680,7 +7680,7 @@
       <c r="F275" s="7"/>
       <c r="G275" s="15"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>543</v>
       </c>
@@ -7697,7 +7697,7 @@
       <c r="F276" s="7"/>
       <c r="G276" s="15"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>545</v>
       </c>
@@ -7714,7 +7714,7 @@
       <c r="F277" s="7"/>
       <c r="G277" s="15"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>547</v>
       </c>
@@ -7731,7 +7731,7 @@
       <c r="F278" s="7"/>
       <c r="G278" s="15"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>549</v>
       </c>
@@ -7748,7 +7748,7 @@
       <c r="F279" s="7"/>
       <c r="G279" s="15"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>551</v>
       </c>
@@ -7765,7 +7765,7 @@
       <c r="F280" s="7"/>
       <c r="G280" s="15"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>553</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="F281" s="7"/>
       <c r="G281" s="15"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>555</v>
       </c>
@@ -7799,7 +7799,7 @@
       <c r="F282" s="7"/>
       <c r="G282" s="15"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>557</v>
       </c>
@@ -7816,7 +7816,7 @@
       <c r="F283" s="7"/>
       <c r="G283" s="15"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>559</v>
       </c>
@@ -7833,7 +7833,7 @@
       <c r="F284" s="7"/>
       <c r="G284" s="15"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>561</v>
       </c>
@@ -7850,7 +7850,7 @@
       <c r="F285" s="7"/>
       <c r="G285" s="15"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>563</v>
       </c>
@@ -7867,7 +7867,7 @@
       <c r="F286" s="7"/>
       <c r="G286" s="15"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>565</v>
       </c>
@@ -7884,7 +7884,7 @@
       <c r="F287" s="7"/>
       <c r="G287" s="15"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>567</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="F288" s="7"/>
       <c r="G288" s="15"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>569</v>
       </c>
@@ -7918,7 +7918,7 @@
       <c r="F289" s="7"/>
       <c r="G289" s="15"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>571</v>
       </c>
@@ -7935,7 +7935,7 @@
       <c r="F290" s="7"/>
       <c r="G290" s="15"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>573</v>
       </c>
@@ -7952,7 +7952,7 @@
       <c r="F291" s="7"/>
       <c r="G291" s="15"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>575</v>
       </c>
@@ -7969,7 +7969,7 @@
       <c r="F292" s="7"/>
       <c r="G292" s="15"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>577</v>
       </c>
@@ -7986,7 +7986,7 @@
       <c r="F293" s="7"/>
       <c r="G293" s="15"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>579</v>
       </c>
@@ -8003,7 +8003,7 @@
       <c r="F294" s="7"/>
       <c r="G294" s="15"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>581</v>
       </c>
@@ -8020,7 +8020,7 @@
       <c r="F295" s="7"/>
       <c r="G295" s="15"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>583</v>
       </c>
@@ -8037,7 +8037,7 @@
       <c r="F296" s="7"/>
       <c r="G296" s="15"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>585</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="F297" s="7"/>
       <c r="G297" s="15"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>587</v>
       </c>
@@ -8071,7 +8071,7 @@
       <c r="F298" s="7"/>
       <c r="G298" s="15"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>589</v>
       </c>
@@ -8088,7 +8088,7 @@
       <c r="F299" s="7"/>
       <c r="G299" s="15"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>315</v>
       </c>
@@ -8105,7 +8105,7 @@
       <c r="F300" s="7"/>
       <c r="G300" s="15"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>315</v>
       </c>
@@ -8122,7 +8122,7 @@
       <c r="F301" s="7"/>
       <c r="G301" s="15"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>315</v>
       </c>
@@ -8139,7 +8139,7 @@
       <c r="F302" s="7"/>
       <c r="G302" s="15"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>315</v>
       </c>
@@ -8156,7 +8156,7 @@
       <c r="F303" s="7"/>
       <c r="G303" s="15"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>315</v>
       </c>
@@ -8173,7 +8173,7 @@
       <c r="F304" s="7"/>
       <c r="G304" s="15"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="4"/>
       <c r="B305" s="5" t="s">
         <v>601</v>
@@ -8188,7 +8188,7 @@
       <c r="F305" s="7"/>
       <c r="G305" s="15"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="4"/>
       <c r="B306" s="5" t="s">
         <v>602</v>
@@ -8203,7 +8203,7 @@
       <c r="F306" s="7"/>
       <c r="G306" s="15"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="4"/>
       <c r="B307" s="5" t="s">
         <v>603</v>
@@ -8218,7 +8218,7 @@
       <c r="F307" s="7"/>
       <c r="G307" s="15"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="4"/>
       <c r="B308" s="5" t="s">
         <v>604</v>
@@ -8233,7 +8233,7 @@
       <c r="F308" s="7"/>
       <c r="G308" s="15"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="4"/>
       <c r="B309" s="5" t="s">
         <v>605</v>
@@ -8248,7 +8248,7 @@
       <c r="F309" s="7"/>
       <c r="G309" s="15"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="4"/>
       <c r="B310" s="5" t="s">
         <v>606</v>
@@ -8263,7 +8263,7 @@
       <c r="F310" s="7"/>
       <c r="G310" s="15"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="4"/>
       <c r="B311" s="5" t="s">
         <v>607</v>
@@ -8278,7 +8278,7 @@
       <c r="F311" s="7"/>
       <c r="G311" s="15"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="4"/>
       <c r="B312" s="5" t="s">
         <v>608</v>
@@ -8293,7 +8293,7 @@
       <c r="F312" s="7"/>
       <c r="G312" s="15"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="4"/>
       <c r="B313" s="5" t="s">
         <v>609</v>
@@ -8308,7 +8308,7 @@
       <c r="F313" s="7"/>
       <c r="G313" s="15"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="4"/>
       <c r="B314" s="5" t="s">
         <v>611</v>
@@ -8323,7 +8323,7 @@
       <c r="F314" s="7"/>
       <c r="G314" s="15"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="4"/>
       <c r="B315" s="5" t="s">
         <v>612</v>
@@ -8360,13 +8360,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EBB0ED-F0A4-451D-A0CC-9086E3F9A531}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>552</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>566</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>570</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>591</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>554</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>556</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>592</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>580</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>576</v>
       </c>
@@ -8438,7 +8438,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>572</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>593</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>594</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
         <v>558</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
         <v>560</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>562</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
         <v>595</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
         <v>582</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
         <v>568</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
         <v>564</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="16" t="s">
         <v>574</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="16" t="s">
         <v>584</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="16" t="s">
         <v>586</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="16" t="s">
         <v>588</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16" t="s">
         <v>578</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
         <v>590</v>
       </c>
